--- a/docs/StructureDefinition-days-until-next-examination-extension.xlsx
+++ b/docs/StructureDefinition-days-until-next-examination-extension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-30T22:57:21+01:00</t>
+    <t>2025-12-18T07:21:20+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-days-until-next-examination-extension.xlsx
+++ b/docs/StructureDefinition-days-until-next-examination-extension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T09:57:13+01:00</t>
+    <t>2026-03-31T17:09:32+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-days-until-next-examination-extension.xlsx
+++ b/docs/StructureDefinition-days-until-next-examination-extension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.8.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T17:09:32+02:00</t>
+    <t>2026-04-17T16:52:07+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-days-until-next-examination-extension.xlsx
+++ b/docs/StructureDefinition-days-until-next-examination-extension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.0</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T16:52:07+02:00</t>
+    <t>2026-05-08T13:22:39+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-days-until-next-examination-extension.xlsx
+++ b/docs/StructureDefinition-days-until-next-examination-extension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T13:22:39+02:00</t>
+    <t>2026-06-05T15:47:27+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-days-until-next-examination-extension.xlsx
+++ b/docs/StructureDefinition-days-until-next-examination-extension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T15:47:27+02:00</t>
+    <t>2026-06-08T15:50:57+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
